--- a/8306.T_report.xlsx
+++ b/8306.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,10 +449,30 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
@@ -464,68 +484,715 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>2022-02-02</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-03-01</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>614</v>
+      </c>
+      <c r="E2" t="n">
+        <v>597.26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1973</v>
+      </c>
+      <c r="I2" t="n">
+        <v>970767</v>
+      </c>
+      <c r="J2" t="n">
+        <v>27</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>総取引回数</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-03-16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-03-22</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>631.9299999999999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>685.21</v>
+      </c>
+      <c r="F3" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="G3" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1050594</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>勝率</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-12-19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2022-12-21</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>687.77</v>
+      </c>
+      <c r="E4" t="n">
+        <v>756</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2205</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1152606</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>総利益率</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>59.87%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-11-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2023-11-08</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1192.05</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1111.43</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-6.76</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-6.96</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2227</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1072427</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>平均保有日数</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>11.6日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2024-04-26</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1450.77</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1546.26</v>
+      </c>
+      <c r="F6" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2215</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1140800</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1598738</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-01-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1767.48</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1876.83</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2352</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1209029</v>
+      </c>
+      <c r="J7" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>598738</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-02-19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025-02-21</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1911.96</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1849.32</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.47</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2378</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1167044</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>41528</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025-03-21</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1901.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2111.62</v>
+      </c>
+      <c r="F9" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2463</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1293537</v>
+      </c>
+      <c r="J9" t="n">
+        <v>7</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-08-04</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1981.17</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2147.69</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8.41</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2696</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1399568</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2167.48</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2125.48</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.94</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2772</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1369675</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2253.16</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2401.57</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.38</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2830</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1457066</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2303.25</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2473.62</v>
+      </c>
+      <c r="F13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3022</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1561822</v>
+      </c>
+      <c r="J13" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2484.47</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2390.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.79</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3064</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1499562</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2572.37</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2727.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3089</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1586619</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2904.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2775.04</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3102</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1512618</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>2929</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3553</v>
-      </c>
-      <c r="F2" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>67</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>総取引回数</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>勝率</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>総利益率</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>21.30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>平均保有日数</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>67.0日</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>2931.93</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3104.89</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3114</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1598738</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>take_profit</t>
         </is>
       </c>
     </row>

--- a/8306.T_report.xlsx
+++ b/8306.T_report.xlsx
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1598738</v>
+        <v>1598737</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>598738</v>
+        <v>598737</v>
       </c>
     </row>
     <row r="8">
@@ -808,7 +808,7 @@
         <v>2378</v>
       </c>
       <c r="I8" t="n">
-        <v>1167044</v>
+        <v>1167043</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
@@ -898,7 +898,7 @@
         <v>2696</v>
       </c>
       <c r="I10" t="n">
-        <v>1399568</v>
+        <v>1399567</v>
       </c>
       <c r="J10" t="n">
         <v>8</v>
@@ -980,7 +980,7 @@
         <v>2830</v>
       </c>
       <c r="I12" t="n">
-        <v>1457066</v>
+        <v>1457065</v>
       </c>
       <c r="J12" t="n">
         <v>8</v>
@@ -1062,7 +1062,7 @@
         <v>3064</v>
       </c>
       <c r="I14" t="n">
-        <v>1499562</v>
+        <v>1499561</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
@@ -1185,7 +1185,7 @@
         <v>3114</v>
       </c>
       <c r="I17" t="n">
-        <v>1598738</v>
+        <v>1598737</v>
       </c>
       <c r="J17" t="n">
         <v>4</v>
